--- a/presentation/MGS-Traceability-Schema.xlsx
+++ b/presentation/MGS-Traceability-Schema.xlsx
@@ -2804,7 +2804,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>เวอร์ชันโครงสร้าง 2026.08.22-1 · 23 ตาราง · 325 คอลัมน์ · สร้างจาก apps-script/traceability/00_Config.gs โดยตรง</t>
+          <t>เวอร์ชันโครงสร้าง 2026.08.22-2 · 23 ตาราง · 325 คอลัมน์ · สร้างจาก apps-script/traceability/00_Config.gs โดยตรง</t>
         </is>
       </c>
     </row>
